--- a/assets/1110(1)(1).xlsx
+++ b/assets/1110(1)(1).xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>2018年底</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>净利息收益率（NIM）（%）</t>
-  </si>
-  <si>
-    <t>手工输入</t>
   </si>
   <si>
     <t>存贷比（%）</t>
@@ -197,7 +194,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,13 +206,6 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -601,7 +591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -647,39 +637,6 @@
       <right style="medium">
         <color rgb="FF86BDEC"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF86BDEC"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF86BDEC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF86BDEC"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF86BDEC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF86BDEC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF86BDEC"/>
-      </right>
       <top style="medium">
         <color rgb="FF86BDEC"/>
       </top>
@@ -696,6 +653,28 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF86BDEC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF86BDEC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF86BDEC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF86BDEC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -815,137 +794,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -959,44 +938,32 @@
     <xf numFmtId="57" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1113,7 +1080,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1154,7 +1121,7 @@
           <xdr:col>2</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1195,7 +1162,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1236,7 +1203,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1277,7 +1244,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1318,7 +1285,7 @@
           <xdr:col>4</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1359,7 +1326,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1400,7 +1367,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1441,7 +1408,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1482,7 +1449,7 @@
           <xdr:col>6</xdr:col>
           <xdr:colOff>257175</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
+          <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
@@ -1800,7 +1767,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="8" max="8" width="10.7818181818182"/>
@@ -1848,550 +1815,298 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
+    <row r="2" ht="14.75" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10"/>
     </row>
-    <row r="3" ht="14.75" spans="1:14">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="9"/>
+    <row r="3" ht="27.75" spans="1:14">
+      <c r="A3" s="11"/>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="13" t="s">
-        <v>5</v>
-      </c>
+    <row r="4" ht="14.75" spans="1:14">
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="14">
-        <v>651.86</v>
-      </c>
-      <c r="D4" s="14">
-        <v>707.38</v>
-      </c>
-      <c r="E4" s="15">
-        <v>788.17</v>
-      </c>
-      <c r="F4" s="14">
-        <v>863.41</v>
-      </c>
-      <c r="G4" s="15">
-        <v>928.49</v>
-      </c>
-      <c r="H4" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" ht="27.75" spans="1:14">
-      <c r="A5" s="8"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="14">
-        <v>354.28</v>
-      </c>
-      <c r="D5" s="14">
-        <v>391.38</v>
-      </c>
-      <c r="E5" s="15">
-        <v>452.32</v>
-      </c>
-      <c r="F5" s="14">
-        <v>490.38</v>
-      </c>
-      <c r="G5" s="15">
-        <v>552.24</v>
-      </c>
-      <c r="H5" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="8"/>
+    <row r="6" ht="27.75" spans="1:14">
+      <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="14">
-        <v>584.56</v>
-      </c>
-      <c r="D6" s="14">
-        <v>635.18</v>
-      </c>
-      <c r="E6" s="15">
-        <v>711.55</v>
-      </c>
-      <c r="F6" s="14">
-        <v>786.97</v>
-      </c>
-      <c r="G6" s="15">
-        <v>847.83</v>
-      </c>
-      <c r="H6" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
     </row>
     <row r="7" ht="27.75" spans="1:14">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="14">
-        <v>487.5</v>
-      </c>
-      <c r="D7" s="14">
-        <v>553.27</v>
-      </c>
-      <c r="E7" s="15">
-        <v>602.63</v>
-      </c>
-      <c r="F7" s="14">
-        <v>637.57</v>
-      </c>
-      <c r="G7" s="15">
-        <v>709.38</v>
-      </c>
-      <c r="H7" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" ht="27.75" spans="1:14">
-      <c r="A8" s="3"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="14">
-        <v>6.1</v>
-      </c>
-      <c r="D8" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="E8" s="15">
-        <v>3.51</v>
-      </c>
-      <c r="F8" s="14">
-        <v>3.02</v>
-      </c>
-      <c r="G8" s="15">
-        <v>3.27</v>
-      </c>
-      <c r="H8" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10"/>
     </row>
-    <row r="9" ht="27.75" spans="1:14">
-      <c r="A9" s="13" t="s">
-        <v>11</v>
-      </c>
+    <row r="9" ht="41.25" spans="1:14">
+      <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="14">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" ht="54.75" spans="1:14">
+      <c r="A10" s="11"/>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" ht="27.75" spans="1:14">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" ht="41.25" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" ht="41.25" spans="1:14">
+      <c r="A13" s="11"/>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" ht="27.75" spans="1:14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="14">
-        <v>20.13</v>
-      </c>
-      <c r="E9" s="15">
-        <v>10.18</v>
-      </c>
-      <c r="F9" s="14">
-        <v>19.78</v>
-      </c>
-      <c r="G9" s="15">
-        <v>8.78</v>
-      </c>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" ht="27.75" spans="1:14">
-      <c r="A10" s="8"/>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="14">
-        <v>5.82</v>
-      </c>
-      <c r="D10" s="14">
-        <v>6.35</v>
-      </c>
-      <c r="E10" s="15">
-        <v>3.19</v>
-      </c>
-      <c r="F10" s="14">
-        <v>6.55</v>
-      </c>
-      <c r="G10" s="15">
-        <v>3.11</v>
-      </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" ht="41.25" spans="1:14">
-      <c r="A11" s="8"/>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="16">
-        <v>0.92</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.93</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0.82</v>
-      </c>
-      <c r="F11" s="16">
-        <v>0.83</v>
-      </c>
-      <c r="G11" s="15">
-        <v>0.71</v>
-      </c>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" ht="54.75" spans="1:14">
-      <c r="A12" s="8"/>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="16">
-        <v>9.05</v>
-      </c>
-      <c r="D12" s="16">
-        <v>9.1</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="16">
-        <v>8.81</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" ht="27.75" spans="1:14">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="16">
-        <v>74.55</v>
-      </c>
-      <c r="D13" s="16">
-        <v>69.71</v>
-      </c>
-      <c r="E13" s="15">
-        <v>71.11</v>
-      </c>
-      <c r="F13" s="16">
-        <v>76.99</v>
-      </c>
-      <c r="G13" s="15">
-        <v>73.01</v>
-      </c>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" ht="41.25" spans="1:14">
-      <c r="A14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="16">
-        <v>6.21</v>
-      </c>
-      <c r="D14" s="16">
-        <v>5.85</v>
-      </c>
-      <c r="E14" s="15">
-        <v>29.97</v>
-      </c>
-      <c r="F14" s="16">
-        <v>5.48</v>
-      </c>
-      <c r="G14" s="15">
-        <v>26.37</v>
-      </c>
-      <c r="H14" s="9"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" ht="41.25" spans="1:14">
-      <c r="A15" s="8"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="16">
-        <v>6.21</v>
-      </c>
-      <c r="D15" s="16">
-        <v>5.85</v>
-      </c>
-      <c r="E15" s="15">
-        <v>5.69</v>
-      </c>
-      <c r="F15" s="16">
-        <v>5.48</v>
-      </c>
-      <c r="G15" s="15">
-        <v>5.14</v>
-      </c>
-      <c r="H15" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" ht="27.75" spans="1:14">
-      <c r="A16" s="8"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="16">
-        <v>14.67</v>
-      </c>
-      <c r="D16" s="16">
-        <v>16.27</v>
-      </c>
-      <c r="E16" s="15">
-        <v>14.75</v>
-      </c>
-      <c r="F16" s="16">
-        <v>14.68</v>
-      </c>
-      <c r="G16" s="15">
-        <v>15.17</v>
-      </c>
-      <c r="H16" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="10"/>
+      <c r="K16" s="13"/>
     </row>
-    <row r="17" ht="41.25" spans="1:11">
-      <c r="A17" s="8"/>
+    <row r="17" ht="27.75" spans="1:8">
+      <c r="A17" s="11"/>
       <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="16">
-        <v>13.52</v>
-      </c>
-      <c r="D17" s="16">
-        <v>15.13</v>
-      </c>
-      <c r="E17" s="15">
-        <v>13.6</v>
-      </c>
-      <c r="F17" s="16">
-        <v>13.53</v>
-      </c>
-      <c r="G17" s="15">
-        <v>14.02</v>
-      </c>
-      <c r="H17" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="10"/>
     </row>
-    <row r="18" ht="27.75" spans="1:11">
-      <c r="A18" s="8"/>
+    <row r="18" ht="41.25" spans="1:8">
+      <c r="A18" s="11"/>
       <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="16">
-        <v>370.19</v>
-      </c>
-      <c r="D18" s="16">
-        <v>516.03</v>
-      </c>
-      <c r="E18" s="15">
-        <v>451.37</v>
-      </c>
-      <c r="F18" s="16">
-        <v>425.07</v>
-      </c>
-      <c r="G18" s="15">
-        <v>501.59</v>
-      </c>
-      <c r="H18" s="9"/>
-      <c r="I18"/>
-      <c r="J18"/>
-      <c r="K18" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="10"/>
     </row>
-    <row r="19" ht="27.75" spans="1:11">
-      <c r="A19" s="8"/>
+    <row r="19" ht="68.25" spans="1:8">
+      <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1.7</v>
-      </c>
-      <c r="D19" s="16">
-        <v>1.13</v>
-      </c>
-      <c r="E19" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="F19" s="16">
-        <v>1.18</v>
-      </c>
-      <c r="G19" s="15">
-        <v>0.93</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="10"/>
     </row>
-    <row r="20" ht="41.25" spans="1:11">
-      <c r="A20" s="8"/>
+    <row r="20" ht="14.75" spans="1:8">
+      <c r="A20" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="16">
-        <v>4.05</v>
-      </c>
-      <c r="D20" s="16">
-        <v>2.46</v>
-      </c>
-      <c r="E20" s="15">
-        <v>5.13</v>
-      </c>
-      <c r="F20" s="16">
-        <v>6.11</v>
-      </c>
-      <c r="G20" s="15">
-        <v>4.49</v>
-      </c>
-      <c r="H20" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10"/>
     </row>
-    <row r="21" ht="68.25" spans="1:11">
-      <c r="A21" s="3"/>
+    <row r="21" ht="27.75" spans="1:8">
+      <c r="A21" s="11"/>
       <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1.07</v>
-      </c>
-      <c r="D21" s="16">
-        <v>0.59</v>
-      </c>
-      <c r="E21" s="15">
-        <v>1.13</v>
-      </c>
-      <c r="F21" s="16">
-        <v>1.18</v>
-      </c>
-      <c r="G21" s="15">
-        <v>0.81</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="13" t="s">
-        <v>27</v>
-      </c>
+    <row r="22" ht="27.75" spans="1:8">
+      <c r="A22" s="11"/>
       <c r="B22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="16">
-        <v>71.52</v>
-      </c>
-      <c r="D22" s="16">
-        <v>76.96</v>
-      </c>
-      <c r="E22" s="15">
-        <v>68.03</v>
-      </c>
-      <c r="F22" s="16">
-        <v>50.94</v>
-      </c>
-      <c r="G22" s="15">
-        <v>35.94</v>
-      </c>
-      <c r="H22" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="10"/>
     </row>
-    <row r="23" ht="27.75" spans="1:11">
-      <c r="A23" s="8"/>
+    <row r="23" ht="27.75" spans="1:8">
+      <c r="A23" s="11"/>
       <c r="B23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="10"/>
     </row>
-    <row r="24" ht="27.75" spans="1:11">
-      <c r="A24" s="8"/>
+    <row r="24" ht="41.25" spans="1:8">
+      <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" ht="27.75" spans="1:11">
-      <c r="A25" s="8"/>
-      <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="16">
-        <v>113.76</v>
-      </c>
-      <c r="D25" s="16">
-        <v>157</v>
-      </c>
-      <c r="E25" s="15">
-        <v>157.44</v>
-      </c>
-      <c r="F25" s="16">
-        <v>158.89</v>
-      </c>
-      <c r="G25" s="15">
-        <v>158.27</v>
-      </c>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" ht="41.25" spans="1:11">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="18">
-        <v>100.64</v>
-      </c>
-      <c r="D26" s="18">
-        <v>154.86</v>
-      </c>
-      <c r="E26" s="19">
-        <v>116.22</v>
-      </c>
-      <c r="F26" s="18">
-        <v>134.88</v>
-      </c>
-      <c r="G26" s="19">
-        <v>108.84</v>
-      </c>
-      <c r="H26" s="20"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A20:A24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2414,7 +2129,7 @@
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2439,7 +2154,7 @@
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2464,7 +2179,7 @@
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2489,7 +2204,7 @@
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2514,7 +2229,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2539,7 +2254,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2564,7 +2279,7 @@
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2589,7 +2304,7 @@
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2614,7 +2329,7 @@
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -2639,7 +2354,7 @@
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>47625</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
